--- a/excel/OutreachHours.xlsx
+++ b/excel/OutreachHours.xlsx
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
